--- a/从零开始学Slots/从零开始学Slots-12-数值篇-Scatter(4).xlsx
+++ b/从零开始学Slots/从零开始学Slots-12-数值篇-Scatter(4).xlsx
@@ -6333,6 +6333,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N129" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -7049,5 +7052,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M73" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-12-数值篇-Scatter(4).xlsx
+++ b/从零开始学Slots/从零开始学Slots-12-数值篇-Scatter(4).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
     <r>
       <rPr>
@@ -5431,7 +5431,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5562,6 +5562,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6411,8 +6415,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>95</v>
+      <c r="A7" s="33">
+        <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>96</v>
@@ -6967,8 +6971,8 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16" t="s">
-        <v>138</v>
+      <c r="A48" s="33">
+        <v>5</v>
       </c>
       <c r="B48" s="23" t="str">
         <f aca="false">IF(2^(3*5)=32768,"✓","✗")</f>

--- a/从零开始学Slots/从零开始学Slots-12-数值篇-Scatter(4).xlsx
+++ b/从零开始学Slots/从零开始学Slots-12-数值篇-Scatter(4).xlsx
@@ -5249,12 +5249,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -5431,7 +5432,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5565,6 +5566,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6511,7 +6520,7 @@
       <c r="A15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="35" t="n">
         <f aca="false">BINOMDIST(A15,$B$9,$B$10,FALSE())</f>
         <v>0.463291230159753</v>
       </c>
@@ -6527,7 +6536,7 @@
       <c r="A16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="35" t="n">
         <f aca="false">BINOMDIST(A16,$B$9,$B$10,FALSE())</f>
         <v>0.365756234336647</v>
       </c>
@@ -6543,7 +6552,7 @@
       <c r="A17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="35" t="n">
         <f aca="false">BINOMDIST(A17,$B$9,$B$10,FALSE())</f>
         <v>0.13475229686087</v>
       </c>
@@ -6559,7 +6568,7 @@
       <c r="A18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="35" t="n">
         <f aca="false">BINOMDIST(A18,$B$9,$B$10,FALSE())</f>
         <v>0.0307329799858125</v>
       </c>
@@ -6575,7 +6584,7 @@
       <c r="A19" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="35" t="n">
         <f aca="false">BINOMDIST(A19,$B$9,$B$10,FALSE())</f>
         <v>0.00485257578723355</v>
       </c>
@@ -6591,7 +6600,7 @@
       <c r="A20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="35" t="n">
         <f aca="false">BINOMDIST(A20,$B$9,$B$10,FALSE())</f>
         <v>0.000561877196416516</v>
       </c>
@@ -6607,7 +6616,7 @@
       <c r="A21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="35" t="n">
         <f aca="false">BINOMDIST(A21,$B$9,$B$10,FALSE())</f>
         <v>4.92874733698699E-005</v>
       </c>
@@ -6623,7 +6632,7 @@
       <c r="A22" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="35" t="n">
         <f aca="false">BINOMDIST(A22,$B$9,$B$10,FALSE())</f>
         <v>3.33524255886337E-006</v>
       </c>
@@ -6639,7 +6648,7 @@
       <c r="A23" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="35" t="n">
         <f aca="false">BINOMDIST(A23,$B$9,$B$10,FALSE())</f>
         <v>1.75539082045441E-007</v>
       </c>
@@ -6655,7 +6664,7 @@
       <c r="A24" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="35" t="n">
         <f aca="false">BINOMDIST(A24,$B$9,$B$10,FALSE())</f>
         <v>7.18581037612916E-009</v>
       </c>
@@ -6671,7 +6680,7 @@
       <c r="A25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="35" t="n">
         <f aca="false">BINOMDIST(A25,$B$9,$B$10,FALSE())</f>
         <v>2.26920327667236E-010</v>
       </c>
@@ -6687,7 +6696,7 @@
       <c r="A26" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="35" t="n">
         <f aca="false">BINOMDIST(A26,$B$9,$B$10,FALSE())</f>
         <v>5.4287159729004E-012</v>
       </c>
@@ -6703,7 +6712,7 @@
       <c r="A27" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="35" t="n">
         <f aca="false">BINOMDIST(A27,$B$9,$B$10,FALSE())</f>
         <v>9.52406311035157E-014</v>
       </c>
@@ -6719,7 +6728,7 @@
       <c r="A28" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="35" t="n">
         <f aca="false">BINOMDIST(A28,$B$9,$B$10,FALSE())</f>
         <v>1.15676879882813E-015</v>
       </c>
@@ -6735,7 +6744,7 @@
       <c r="A29" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="35" t="n">
         <f aca="false">BINOMDIST(A29,$B$9,$B$10,FALSE())</f>
         <v>8.69750976562501E-018</v>
       </c>
@@ -6751,7 +6760,7 @@
       <c r="A30" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="35" t="n">
         <f aca="false">BINOMDIST(A30,$B$9,$B$10,FALSE())</f>
         <v>3.0517578125E-020</v>
       </c>
@@ -6767,7 +6776,7 @@
       <c r="A31" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="35" t="n">
         <f aca="false">SUM(B15:B30)</f>
         <v>0.999999999999999</v>
       </c>
@@ -6779,7 +6788,7 @@
       <c r="A32" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="35" t="n">
         <f aca="false">1-BINOMDIST($B$11-1,$B$9,$B$10,TRUE())</f>
         <v>0.0362002386427298</v>
       </c>
